--- a/Vul_Assessment_Framework_forRAG_apps.xlsx
+++ b/Vul_Assessment_Framework_forRAG_apps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/481edc4588b61275/AI_Research/2025/GenAI/AI_Risk_Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{F2D28FEC-7A35-4481-8FCA-BA405FC8A303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A0D50F4-6C7B-44E3-9DBE-6DFF7D238FAB}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{F2D28FEC-7A35-4481-8FCA-BA405FC8A303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD955A70-B5F5-44F9-906B-DCF4E09AC916}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{3EC62E44-B4D5-4773-ABE4-69A89A4801C2}"/>
   </bookViews>
@@ -57,10 +57,47 @@
     <t>Architecture Analysis</t>
   </si>
   <si>
-    <t>• Map out complete workflow from user input to final output&lt;br&gt;• Identify all components in the architecture&lt;br&gt;• Document data flow paths and integration points</t>
-  </si>
-  <si>
-    <t>• Draw.io (diagram creation)&lt;br&gt;• OWASP Threat Dragon&lt;br&gt;• PlantUML for architecture visualization</t>
+    <t>Input Validation Testing</t>
+  </si>
+  <si>
+    <t>Information Retrieval Security</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Authorization</t>
+  </si>
+  <si>
+    <t>Data Leakage Testing</t>
+  </si>
+  <si>
+    <t>Integration Security</t>
+  </si>
+  <si>
+    <t>Output Filtering</t>
+  </si>
+  <si>
+    <t>Prompt Engineering Attacks</t>
+  </si>
+  <si>
+    <t>Rate Limiting &amp; Resource Abuse</t>
+  </si>
+  <si>
+    <t>Logging &amp; Monitoring</t>
+  </si>
+  <si>
+    <t>Report Documentation</t>
+  </si>
+  <si>
+    <t>Vulnerability Assessment Framework for RAG Applications</t>
+  </si>
+  <si>
+    <t>• Map out complete workflow from user input to final output
+• Identify all components in the architecture
+• Document data flow paths and integration points</t>
+  </si>
+  <si>
+    <t>• Draw.io (diagram creation)
+• OWASP Threat Dragon
+• PlantUML for architecture visualization</t>
   </si>
   <si>
     <r>
@@ -85,7 +122,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Create visual diagrams of your RAG pipeline to identify potential threat vectors&lt;br&gt;• </t>
+      <t xml:space="preserve">: Create visual diagrams of your RAG pipeline to identify potential threat vectors
+• </t>
     </r>
     <r>
       <rPr>
@@ -106,7 +144,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Model threats using STRIDE methodology&lt;br&gt;</t>
+      <t xml:space="preserve">: Model threats using STRIDE methodology
+</t>
     </r>
     <r>
       <rPr>
@@ -131,13 +170,16 @@
     </r>
   </si>
   <si>
-    <t>Input Validation Testing</t>
-  </si>
-  <si>
-    <t>• Test for prompt injection vulnerabilities&lt;br&gt;• Check input sanitization mechanisms&lt;br&gt;• Try inserting system prompts or instructions&lt;br&gt;• Test with code snippets, special characters, and unusual formatting</t>
-  </si>
-  <si>
-    <t>• GPTFuzz&lt;br&gt;• Garak&lt;br&gt;• LLM Guard&lt;br&gt;• Rebuff Framework</t>
+    <t>• Test for prompt injection vulnerabilities
+• Check input sanitization mechanisms
+• Try inserting system prompts or instructions
+• Test with code snippets, special characters, and unusual formatting</t>
+  </si>
+  <si>
+    <t>• GPTFuzz
+• Garak
+• LLM Guard
+• Rebuff Framework</t>
   </si>
   <si>
     <r>
@@ -162,7 +204,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Automatically generate thousands of malicious inputs to test boundaries&lt;br&gt;• </t>
+      <t xml:space="preserve">: Automatically generate thousands of malicious inputs to test boundaries
+• </t>
     </r>
     <r>
       <rPr>
@@ -183,7 +226,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Run predefined prompt injection attacks&lt;br&gt;</t>
+      <t xml:space="preserve">: Run predefined prompt injection attacks
+</t>
     </r>
     <r>
       <rPr>
@@ -234,13 +278,16 @@
     </r>
   </si>
   <si>
-    <t>Information Retrieval Security</t>
-  </si>
-  <si>
-    <t>• Verify authorization controls for document access&lt;br&gt;• Test for unauthorized information access&lt;br&gt;• Check if document boundaries are properly enforced&lt;br&gt;• Attempt restricted information retrieval through semantic similarity</t>
-  </si>
-  <si>
-    <t>• OWASP ZAP&lt;br&gt;• Langchain Security Tooling&lt;br&gt;• LLMSecurity Scanner&lt;br&gt;• Metasploit (with custom modules)</t>
+    <t>• Verify authorization controls for document access
+• Test for unauthorized information access
+• Check if document boundaries are properly enforced
+• Attempt restricted information retrieval through semantic similarity</t>
+  </si>
+  <si>
+    <t>• OWASP ZAP
+• Langchain Security Tooling
+• LLMSecurity Scanner
+• Metasploit (with custom modules)</t>
   </si>
   <si>
     <r>
@@ -265,7 +312,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Intercept and modify API calls to the retrieval system&lt;br&gt;• </t>
+      <t xml:space="preserve">: Intercept and modify API calls to the retrieval system
+• </t>
     </r>
     <r>
       <rPr>
@@ -286,7 +334,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Test vector database access controls&lt;br&gt;</t>
+      <t xml:space="preserve">: Test vector database access controls
+</t>
     </r>
     <r>
       <rPr>
@@ -319,13 +368,16 @@
     </r>
   </si>
   <si>
-    <t>Authentication &amp; Authorization</t>
-  </si>
-  <si>
-    <t>• Verify authentication on all API endpoints&lt;br&gt;• Check authorization controls around document access&lt;br&gt;• Test user permission enforcement during retrieval&lt;br&gt;• Identify privilege escalation paths</t>
-  </si>
-  <si>
-    <t>• OWASP ZAP&lt;br&gt;• Burp Suite Community Edition&lt;br&gt;• JWT Tool&lt;br&gt;• Authz Playground</t>
+    <t>• Verify authentication on all API endpoints
+• Check authorization controls around document access
+• Test user permission enforcement during retrieval
+• Identify privilege escalation paths</t>
+  </si>
+  <si>
+    <t>• OWASP ZAP
+• Burp Suite Community Edition
+• JWT Tool
+• Authz Playground</t>
   </si>
   <si>
     <r>
@@ -350,7 +402,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Intercept and modify authentication tokens&lt;br&gt;• </t>
+      <t xml:space="preserve">: Intercept and modify authentication tokens
+• </t>
     </r>
     <r>
       <rPr>
@@ -371,7 +424,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Analyze and manipulate JSON Web Tokens&lt;br&gt;</t>
+      <t xml:space="preserve">: Analyze and manipulate JSON Web Tokens
+</t>
     </r>
     <r>
       <rPr>
@@ -432,13 +486,16 @@
     </r>
   </si>
   <si>
-    <t>Data Leakage Testing</t>
-  </si>
-  <si>
-    <t>• Test for training data extraction via targeted prompting&lt;br&gt;• Check if confidential information appears in responses&lt;br&gt;• Verify system details aren't revealed in error messages&lt;br&gt;• Test for model regurgitation of private information</t>
-  </si>
-  <si>
-    <t>• Garak's data leakage modules&lt;br&gt;• LLM Guard&lt;br&gt;• Rebuff&lt;br&gt;• NVD Scanner</t>
+    <t>• Test for training data extraction via targeted prompting
+• Check if confidential information appears in responses
+• Verify system details aren't revealed in error messages
+• Test for model regurgitation of private information</t>
+  </si>
+  <si>
+    <t>• Garak's data leakage modules
+• LLM Guard
+• Rebuff
+• NVD Scanner</t>
   </si>
   <si>
     <r>
@@ -463,7 +520,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Run extraction probes against the model&lt;br&gt;• </t>
+      <t xml:space="preserve">: Run extraction probes against the model
+• </t>
     </r>
     <r>
       <rPr>
@@ -484,7 +542,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Scan responses for personally identifiable information&lt;br&gt;</t>
+      <t xml:space="preserve">: Scan responses for personally identifiable information
+</t>
     </r>
     <r>
       <rPr>
@@ -535,13 +594,15 @@
     </r>
   </si>
   <si>
-    <t>Integration Security</t>
-  </si>
-  <si>
-    <t>• Assess security of external API integrations&lt;br&gt;• Check authentication in service-to-service communications&lt;br&gt;• Test for server-side request forgery&lt;br&gt;• Verify secure handling of API keys and credentials</t>
-  </si>
-  <si>
-    <t>• OWASP ZAP&lt;br&gt;• Burp Suite Community Edition&lt;br&gt;• SSRF Scanner&lt;br&gt;• Nuclei</t>
+    <t>• Assess security of external API integrations
+• Check authentication in service-to-service communications
+• Test for server-side request forgery
+• Verify secure handling of API keys and credentials</t>
+  </si>
+  <si>
+    <t>• OWASP ZAP
+• Burp Suite Community Edition
+• SSRF Scanner&lt;br&gt;• Nuclei</t>
   </si>
   <si>
     <r>
@@ -566,7 +627,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Test if document retrieval can be hijacked to access internal services&lt;br&gt;• </t>
+      <t xml:space="preserve">: Test if document retrieval can be hijacked to access internal services
+• </t>
     </r>
     <r>
       <rPr>
@@ -587,7 +649,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Run templated tests against API endpoints&lt;br&gt;</t>
+      <t xml:space="preserve">: Run templated tests against API endpoints
+</t>
     </r>
     <r>
       <rPr>
@@ -630,13 +693,16 @@
     </r>
   </si>
   <si>
-    <t>Output Filtering</t>
-  </si>
-  <si>
-    <t>• Check for proper filtering of harmful or confidential outputs&lt;br&gt;• Test consistency in output sanitization&lt;br&gt;• Verify citation information doesn't reveal sensitive metadata&lt;br&gt;• Test prevention of malicious content generation</t>
-  </si>
-  <si>
-    <t>• LLM Guard&lt;br&gt;• Garak&lt;br&gt;• NeMo Guardrails&lt;br&gt;• LangKit</t>
+    <t>• Check for proper filtering of harmful or confidential outputs
+• Test consistency in output sanitization
+• Verify citation information doesn't reveal sensitive metadata
+• Test prevention of malicious content generation</t>
+  </si>
+  <si>
+    <t>• LLM Guard
+• Garak
+• NeMo Guardrails
+• LangKit</t>
   </si>
   <si>
     <r>
@@ -661,7 +727,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Automatically detect and filter sensitive outputs&lt;br&gt;• </t>
+      <t xml:space="preserve">: Automatically detect and filter sensitive outputs
+• </t>
     </r>
     <r>
       <rPr>
@@ -682,7 +749,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Test guardrail effectiveness&lt;br&gt;</t>
+      <t xml:space="preserve">: Test guardrail effectiveness
+</t>
     </r>
     <r>
       <rPr>
@@ -715,13 +783,16 @@
     </r>
   </si>
   <si>
-    <t>Prompt Engineering Attacks</t>
-  </si>
-  <si>
-    <t>• Try techniques to bypass content filters&lt;br&gt;• Test for jailbreaking vulnerabilities&lt;br&gt;• Attempt indirect prompting to elicit unintended behavior&lt;br&gt;• Check resilience against adversarial prompts</t>
-  </si>
-  <si>
-    <t>• PAIR (Prompt Attack &amp; Injection Recorder)&lt;br&gt;• Jailbreak Chat&lt;br&gt;• GPTFuzz&lt;br&gt;• Gandalf (NCC Group)</t>
+    <t>• Try techniques to bypass content filters
+• Test for jailbreaking vulnerabilities
+• Attempt indirect prompting to elicit unintended behavior
+• Check resilience against adversarial prompts</t>
+  </si>
+  <si>
+    <t>• PAIR (Prompt Attack &amp; Injection Recorder)
+• Jailbreak Chat
+• GPTFuzz
+• Gandalf (NCC Group)</t>
   </si>
   <si>
     <r>
@@ -746,7 +817,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Record and replay successful prompt attacks&lt;br&gt;• </t>
+      <t xml:space="preserve">: Record and replay successful prompt attacks
+• </t>
     </r>
     <r>
       <rPr>
@@ -767,7 +839,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Progressive challenges to bypass restrictions&lt;br&gt;</t>
+      <t xml:space="preserve">: Progressive challenges to bypass restrictions
+</t>
     </r>
     <r>
       <rPr>
@@ -810,13 +883,16 @@
     </r>
   </si>
   <si>
-    <t>Rate Limiting &amp; Resource Abuse</t>
-  </si>
-  <si>
-    <t>• Test for proper rate limiting on all API endpoints&lt;br&gt;• Check for DoS vulnerabilities from complex queries&lt;br&gt;• Verify controls against excessive token usage&lt;br&gt;• Test for query complexity limitations</t>
-  </si>
-  <si>
-    <t>• Locust&lt;br&gt;• JMeter&lt;br&gt;• Siege&lt;br&gt;• Rate Limiter Tester</t>
+    <t>• Test for proper rate limiting on all API endpoints
+• Check for DoS vulnerabilities from complex queries
+• Verify controls against excessive token usage
+• Test for query complexity limitations</t>
+  </si>
+  <si>
+    <t>• Locust
+• Jmeter
+• Siege
+• Rate Limiter Tester</t>
   </si>
   <si>
     <r>
@@ -841,7 +917,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Simulate multiple users hitting endpoints concurrently&lt;br&gt;• </t>
+      <t xml:space="preserve">: Simulate multiple users hitting endpoints concurrently
+• </t>
     </r>
     <r>
       <rPr>
@@ -862,7 +939,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Create complex load testing scenarios&lt;br&gt;</t>
+      <t xml:space="preserve">: Create complex load testing scenarios
+</t>
     </r>
     <r>
       <rPr>
@@ -887,13 +965,16 @@
     </r>
   </si>
   <si>
-    <t>Logging &amp; Monitoring</t>
-  </si>
-  <si>
-    <t>• Verify proper logging of security events&lt;br&gt;• Check if unusual query patterns trigger alerts&lt;br&gt;• Test if attempted exploits are detected and reported&lt;br&gt;• Verify logs don't contain sensitive information</t>
-  </si>
-  <si>
-    <t>• ELK Stack&lt;br&gt;• Prometheus + Grafana&lt;br&gt;• OSSEC&lt;br&gt;• Wazuh</t>
+    <t>• Verify proper logging of security events
+• Check if unusual query patterns trigger alerts
+• Test if attempted exploits are detected and reported
+• Verify logs don't contain sensitive information</t>
+  </si>
+  <si>
+    <t>• ELK Stack
+• Prometheus + Grafana
+• OSSEC
+• Wazuh</t>
   </si>
   <si>
     <r>
@@ -918,7 +999,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Analyze logs for security events and anomalies&lt;br&gt;• </t>
+      <t xml:space="preserve">: Analyze logs for security events and anomalies
+• </t>
     </r>
     <r>
       <rPr>
@@ -939,7 +1021,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Set up alerting for suspicious activities&lt;br&gt;</t>
+      <t xml:space="preserve">: Set up alerting for suspicious activities
+</t>
     </r>
     <r>
       <rPr>
@@ -964,13 +1047,16 @@
     </r>
   </si>
   <si>
-    <t>Report Documentation</t>
-  </si>
-  <si>
-    <t>• Detail discovered vulnerabilities with proof of concept&lt;br&gt;• Classify severity using standard frameworks (CVSS)&lt;br&gt;• Provide remediation recommendations&lt;br&gt;• Include examples of exploitable scenarios</t>
-  </si>
-  <si>
-    <t>• DefectDojo&lt;br&gt;• OWASP Threat Report Generator&lt;br&gt;• Markdown/LaTeX tools&lt;br&gt;• CVSS Calculator</t>
+    <t>• Detail discovered vulnerabilities with proof of concept
+• Classify severity using standard frameworks (CVSS
+• Provide remediation recommendations
+• Include examples of exploitable scenarios</t>
+  </si>
+  <si>
+    <t>• DefectDojo
+• OWASP Threat Report Generator
+• Markdown/LaTeX tools
+• CVSS Calculator</t>
   </si>
   <si>
     <r>
@@ -995,7 +1081,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: Track vulnerabilities throughout assessment&lt;br&gt;• </t>
+      <t xml:space="preserve">: Track vulnerabilities throughout assessment
+• </t>
     </r>
     <r>
       <rPr>
@@ -1016,7 +1103,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Standardize severity ratings&lt;br&gt;</t>
+      <t xml:space="preserve">: Standardize severity ratings
+</t>
     </r>
     <r>
       <rPr>
@@ -1041,32 +1129,136 @@
     </r>
   </si>
   <si>
-    <t>Vulnerability Assessment Framework for RAG Applications</t>
-  </si>
-  <si>
-    <t>Selecting the Right Tools and Techniques for RAG Security Assessment
+    <r>
+      <t xml:space="preserve">Selecting the Right Tools and Techniques for RAG Security Assessment
 When choosing security assessment tools and techniques for your RAG application, several important factors should guide your decision-making process:
-1. Application Architecture Considerations
-Technology Stack: Match tools to your specific tech stack (e.g., Python-based frameworks like Langchain vs. JavaScript implementations)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. Application Architecture Considerations
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Technology Stack: Match tools to your specific tech stack (e.g., Python-based frameworks like Langchain vs. JavaScript implementations)
 Deployment Model: Cloud-hosted solutions require different testing approaches than on-premises deployments
 Integration Complexity: More complex systems with multiple integration points require comprehensive testing suites
-2. Security Assessment Scope and Depth
-Risk Assessment: Focus more resources on high-risk components that handle sensitive data
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. Security Assessment Scope and Depth
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Risk Assessment: Focus more resources on high-risk components that handle sensitive data
 Testing Depth Required: Penetration testing vs. vulnerability scanning vs. code review
 Time Constraints: Some tools require significant setup but provide deeper analysis
-3. Tool-Specific Selection Criteria
-Ease of Integration: How easily the tool fits into your existing workflows and CI/CD pipeline
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">3. Tool-Specific Selection Criteria
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ease of Integration: How easily the tool fits into your existing workflows and CI/CD pipeline
 Community Support: Active development and community help with troubleshooting
 Documentation Quality: Well-documented tools reduce learning curve and implementation time
 Update Frequency: Tools that update regularly to address new LLM vulnerabilities
-4. Practical Examples for Tool Selection
-ScenarioRecommended ToolWhy This Tool?Rapid initial assessmentGarakLightweight, easy setup, covers multiple vulnerability typesDeep dive on prompt injectionGPTFuzz + custom scriptsBetter fuzzing capabilities and customizability for complex applicationsEnterprise environment with compliance needsOWASP ZAP + DefectDojoComprehensive coverage with standardized reporting for complianceDevSecOps integrationRebuff + CI/CD pluginsEasy automation and integration with development workflowsLimited resources/budgetBurp Suite Community + open source LLM-specific toolsCombine general web security with LLM-specific testing
-5. Technique Selection Based on Assessment Goal
-Compliance-Focused: Standardized test cases with comprehensive documentation
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">4. Practical Examples for Tool Selection
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ScenarioRecommended ToolWhy This Tool?Rapid initial assessmentGarakLightweight, easy setup, covers multiple vulnerability typesDeep dive on prompt injectionGPTFuzz + custom scriptsBetter fuzzing capabilities and customizability for complex applicationsEnterprise environment with compliance needsOWASP ZAP + DefectDojoComprehensive coverage with standardized reporting for complianceDevSecOps integrationRebuff + CI/CD pluginsEasy automation and integration with development workflowsLimited resources/budgetBurp Suite Community + open source LLM-specific toolsCombine general web security with LLM-specific testing
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">5. Technique Selection Based on Assessment Goal
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compliance-Focused: Standardized test cases with comprehensive documentation
 Attacker Simulation: Adversarial techniques mimicking real-world attacks
 Security Hardening: Systematic testing of each component with detailed remediation guidance
 Continuous Security: Lightweight automated tests that can run frequently
-Remember that tool selection isn't one-size-fits-all. The best approach often combines multiple tools and techniques tailored to your specific RAG implementation and security requirements.</t>
+Remember that tool selection isn't one-size-fits-all. The best approach often combines multiple tools and techniques tailored to your specific implementation and security requirements.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1111,7 +1303,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1119,24 +1311,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1153,6 +1357,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1482,212 +1690,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.5">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="114">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="128.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="142.5">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="128.25">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="156.75">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="128.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="142.5">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="128.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="142.5">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="142.5">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="128.25">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.5">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="71.25">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="85.5">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="85.5">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="85.5">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="85.5">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="85.5">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="85.5">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="85.5">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="85.5">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="71.25">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="71.25">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1697,525 +1905,696 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AEF6CF-8650-4848-A856-309AE80A0374}">
-  <dimension ref="B2:P31"/>
+  <dimension ref="B2:P41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:16" ht="14.25" customHeight="1">
+      <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
     </row>
     <row r="17" spans="2:16">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
     </row>
     <row r="18" spans="2:16">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
     </row>
     <row r="20" spans="2:16">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
     </row>
     <row r="21" spans="2:16">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
     </row>
     <row r="22" spans="2:16">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
     </row>
     <row r="23" spans="2:16">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
     </row>
     <row r="24" spans="2:16">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
     </row>
     <row r="25" spans="2:16">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
     </row>
     <row r="26" spans="2:16">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="2:16">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="2:16">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="2:16">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="2:16">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="2:16">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="2:16">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="2:16">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="2:16">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+    </row>
+    <row r="41" spans="2:16">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:P31"/>
+    <mergeCell ref="B2:P41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Vul_Assessment_Framework_forRAG_apps.xlsx
+++ b/Vul_Assessment_Framework_forRAG_apps.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/481edc4588b61275/AI_Research/2025/GenAI/AI_Risk_Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{F2D28FEC-7A35-4481-8FCA-BA405FC8A303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD955A70-B5F5-44F9-906B-DCF4E09AC916}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{F2D28FEC-7A35-4481-8FCA-BA405FC8A303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FAA44F4-4A69-4551-97D3-8119BEDB2A43}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{3EC62E44-B4D5-4773-ABE4-69A89A4801C2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{3EC62E44-B4D5-4773-ABE4-69A89A4801C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>Step</t>
   </si>
@@ -1129,8 +1130,83 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Selecting the Right Tools and Techniques for RAG Security Assessment
+    <t>4. Practical Examples for Tool Selection</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Recommended Tool</t>
+  </si>
+  <si>
+    <t>Why This Tool?</t>
+  </si>
+  <si>
+    <t>Rapid initial assessment</t>
+  </si>
+  <si>
+    <t>Garak</t>
+  </si>
+  <si>
+    <t>Lightweight, easy setup, covers multiple vulnerability types</t>
+  </si>
+  <si>
+    <t>Deep dive on prompt injection</t>
+  </si>
+  <si>
+    <t>GPTFuzz + custom scripts</t>
+  </si>
+  <si>
+    <t>Better fuzzing capabilities and customizability for complex applications</t>
+  </si>
+  <si>
+    <t>Enterprise environment with compliance needs</t>
+  </si>
+  <si>
+    <t>OWASP ZAP + DefectDojo</t>
+  </si>
+  <si>
+    <t>Comprehensive coverage with standardized reporting for compliance</t>
+  </si>
+  <si>
+    <t>DevSecOps integration</t>
+  </si>
+  <si>
+    <t>Rebuff + CI/CD plugins</t>
+  </si>
+  <si>
+    <t>Easy automation and integration with development workflows</t>
+  </si>
+  <si>
+    <t>Limited resources/budget</t>
+  </si>
+  <si>
+    <t>Burp Suite Community + open source LLM-specific tools</t>
+  </si>
+  <si>
+    <t>Combine general web security with LLM-specific testing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Selecting the Right Tools and Techniques for RAG Security Assessment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 When choosing security assessment tools and techniques for your RAG application, several important factors should guide your decision-making process:
 </t>
     </r>
@@ -1260,12 +1336,249 @@
 Remember that tool selection isn't one-size-fits-all. The best approach often combines multiple tools and techniques tailored to your specific implementation and security requirements.</t>
     </r>
   </si>
+  <si>
+    <t>Application Examples Across Generative AI Types</t>
+  </si>
+  <si>
+    <t>Application Type</t>
+  </si>
+  <si>
+    <t>Framework Adaptation</t>
+  </si>
+  <si>
+    <t>Key Security Focus</t>
+  </si>
+  <si>
+    <t>Text-to-Image Generation</t>
+  </si>
+  <si>
+    <t>Replace document retrieval steps with image content filtering</t>
+  </si>
+  <si>
+    <t>Output safety and copyright infringement</t>
+  </si>
+  <si>
+    <t>Conversational AI Assistants</t>
+  </si>
+  <si>
+    <t>Less focus on retrieval, more on conversation history security</t>
+  </si>
+  <si>
+    <t>Session management and context preservation</t>
+  </si>
+  <si>
+    <t>Code Generation Tools</t>
+  </si>
+  <si>
+    <t>Emphasize code output validation and package dependency analysis</t>
+  </si>
+  <si>
+    <t>Code injection and vulnerable code generation</t>
+  </si>
+  <si>
+    <t>Content Creation Tools</t>
+  </si>
+  <si>
+    <t>Focus on content output filtering and attribution</t>
+  </si>
+  <si>
+    <t>Plagiarism detection and copyright compliance</t>
+  </si>
+  <si>
+    <t>Applying the Framework to Broader Generative AI Use Cases</t>
+  </si>
+  <si>
+    <t>The vulnerability assessment framework I shared is adaptable to all generative AI applications, not just RAG systems, with some adjustments. Here's how it translates:</t>
+  </si>
+  <si>
+    <t>Universal vs. RAG-Specific Components</t>
+  </si>
+  <si>
+    <t>Universal to All Generative AI Applications:</t>
+  </si>
+  <si>
+    <r>
+      <t>Input Validation Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Prompt injection vulnerabilities exist in any LLM application</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Output Filtering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: All generative AI needs output sanitization</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Prompt Engineering Attacks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Jailbreaking attempts apply to any LLM system</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Rate Limiting &amp; Resource Abuse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Token usage monitoring is universal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Authentication &amp; Authorization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: All AI systems need access controls</t>
+    </r>
+  </si>
+  <si>
+    <t>RAG-Specific Components (Require Modification):</t>
+  </si>
+  <si>
+    <r>
+      <t>Information Retrieval Security</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: For non-RAG applications, this becomes about data source security and trusted information access</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Architecture Analysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: The components will differ based on the application type</t>
+    </r>
+  </si>
+  <si>
+    <t>Framework Extension for Non-RAG Applications</t>
+  </si>
+  <si>
+    <t>For any generative AI application, you should add:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Model-Specific Vulnerabilities</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Each model family (GPT, Llama, etc.) has unique vulnerabilities</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Training Data Protection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Concerns around data used to train or fine-tune models</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Output Copyright Concerns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Intellectual property risks in generated content</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Domain-Specific Safety</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Financial, healthcare, legal domains have specialized security requirements</t>
+    </r>
+  </si>
+  <si>
+    <t>The core principles remain the same - input validation, output validation, proper authentication and authorization, and monitoring - but the specific techniques and tools must be tailored to the application's architecture and use case.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1289,6 +1602,30 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1330,17 +1667,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1357,10 +1710,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1695,206 +2044,206 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="114">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="128.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="142.5">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="128.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="156.75">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="128.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="142.5">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="128.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="142.5">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="142.5">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="128.25">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1905,690 +2254,751 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AEF6CF-8650-4848-A856-309AE80A0374}">
-  <dimension ref="B2:P41"/>
+  <dimension ref="B2:T41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="18" max="20" width="27.06640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:16">
+      <c r="B2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="2:16">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" spans="2:20">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" spans="2:20" ht="23.25">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="R18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="2:16">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="2:16">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="2:16">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="2:16">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="2:16">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="2:16">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="2:16">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="2:16">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="2:16">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="2:16">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="2:16">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="2:16">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="2:16">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="2:16">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="2:16">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="2:16">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="2:16">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="2:16">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" spans="2:16">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="2:16">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="2:16">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="2:16">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="2:16">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="2:16">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="2:16">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="2:16">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-    </row>
-    <row r="29" spans="2:16">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-    </row>
-    <row r="30" spans="2:16">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-    </row>
-    <row r="31" spans="2:16">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="2:16">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="R20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" ht="28.5">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="R21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" ht="42.75">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="R22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="42.75">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="R23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" ht="28.5">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="R24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" ht="28.5">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="R25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" spans="2:20">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" spans="2:20">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" spans="2:20">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" spans="2:20">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" spans="2:20">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" spans="2:20">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
     </row>
     <row r="33" spans="2:16">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
     </row>
     <row r="34" spans="2:16">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
     </row>
     <row r="35" spans="2:16">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
     </row>
     <row r="37" spans="2:16">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
     </row>
     <row r="38" spans="2:16">
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
     </row>
     <row r="39" spans="2:16">
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
     </row>
     <row r="40" spans="2:16">
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
     </row>
     <row r="41" spans="2:16">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2597,4 +3007,181 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56549882-1462-4254-A4C0-D95CECC109B5}">
+  <dimension ref="B2:D40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="4" width="32.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="23.25">
+      <c r="B2" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="28.5">
+      <c r="B4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="28.5">
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="28.5">
+      <c r="B6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="28.5">
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="31.9">
+      <c r="B12" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="23.25">
+      <c r="B16" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="17.649999999999999">
+      <c r="B18" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="17.649999999999999">
+      <c r="B26" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="9"/>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="23.25">
+      <c r="B31" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="9"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>